--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -631,7 +631,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>기계</t>
+          <t>기타 금속 가공제품 제조업</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -988,7 +988,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>담배</t>
+          <t>담배 제조업</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>건강관리장비와용품</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>자동차부품</t>
+          <t>일차전지 및 이차전지 제조업</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>해운사</t>
+          <t>해상 운송업</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>생명보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>생명보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -5705,6 +5705,57 @@
         </is>
       </c>
       <c r="M104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>489981</v>
+      </c>
+      <c r="E105" t="n">
+        <v>146100</v>
+      </c>
+      <c r="F105" t="n">
+        <v>71586.22410000001</v>
+      </c>
+      <c r="G105" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="H105" t="n">
+        <v>93.77</v>
+      </c>
+      <c r="I105" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>기타 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t>O</t>
         </is>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5761,6 +5761,55 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>3474040</v>
+      </c>
+      <c r="E106" t="n">
+        <v>187100</v>
+      </c>
+      <c r="F106" t="n">
+        <v>649992.884</v>
+      </c>
+      <c r="G106" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H106" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -5776,22 +5776,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3474040</v>
+        <v>3496632</v>
       </c>
       <c r="E106" t="n">
-        <v>187100</v>
+        <v>187500</v>
       </c>
       <c r="F106" t="n">
-        <v>649992.884</v>
+        <v>655618.5</v>
       </c>
       <c r="G106" t="n">
         <v>74.59999999999999</v>
       </c>
       <c r="H106" t="n">
-        <v>227.1</v>
+        <v>227.8</v>
       </c>
       <c r="I106" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5810,6 +5810,55 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>3488964</v>
+      </c>
+      <c r="E107" t="n">
+        <v>194600</v>
+      </c>
+      <c r="F107" t="n">
+        <v>678952.3944</v>
+      </c>
+      <c r="G107" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="H107" t="n">
+        <v>240.21</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -5825,22 +5825,22 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3488964</v>
+        <v>3503866</v>
       </c>
       <c r="E107" t="n">
-        <v>194600</v>
+        <v>193600</v>
       </c>
       <c r="F107" t="n">
-        <v>678952.3944</v>
+        <v>678348.4576</v>
       </c>
       <c r="G107" t="n">
-        <v>72.5</v>
+        <v>79.2</v>
       </c>
       <c r="H107" t="n">
-        <v>240.21</v>
+        <v>238.29</v>
       </c>
       <c r="I107" t="n">
-        <v>2.85</v>
+        <v>2.33</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5825,22 +5825,22 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3503866</v>
+        <v>3510137</v>
       </c>
       <c r="E107" t="n">
-        <v>193600</v>
+        <v>193700</v>
       </c>
       <c r="F107" t="n">
-        <v>678348.4576</v>
+        <v>679913.5368999999</v>
       </c>
       <c r="G107" t="n">
         <v>79.2</v>
       </c>
       <c r="H107" t="n">
-        <v>238.29</v>
+        <v>238.64</v>
       </c>
       <c r="I107" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5856,6 +5856,57 @@
       <c r="M107" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>500</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>230947</v>
+      </c>
+      <c r="E108" t="n">
+        <v>246500</v>
+      </c>
+      <c r="F108" t="n">
+        <v>56928.4355</v>
+      </c>
+      <c r="G108" t="n">
+        <v>96</v>
+      </c>
+      <c r="H108" t="n">
+        <v>647.8099999999999</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5910,6 +5910,157 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>500</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>287119</v>
+      </c>
+      <c r="E109" t="n">
+        <v>260500</v>
+      </c>
+      <c r="F109" t="n">
+        <v>74794.49950000001</v>
+      </c>
+      <c r="G109" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="H109" t="n">
+        <v>702.72</v>
+      </c>
+      <c r="I109" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>356483</v>
+      </c>
+      <c r="E110" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F110" t="n">
+        <v>40639.062</v>
+      </c>
+      <c r="G110" t="n">
+        <v>66</v>
+      </c>
+      <c r="H110" t="n">
+        <v>150.83</v>
+      </c>
+      <c r="I110" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>88350</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>5114344</v>
+      </c>
+      <c r="E111" t="n">
+        <v>6010</v>
+      </c>
+      <c r="F111" t="n">
+        <v>30737.20744</v>
+      </c>
+      <c r="G111" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="H111" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>보험업</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -631,7 +631,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>기타 금속 가공제품 제조업</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -988,7 +988,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>담배 제조업</t>
+          <t>담배</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>전기장비</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>건강관리장비와용품</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>IT서비스</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>전기장비</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>IT서비스</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>IT서비스</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>일차전지 및 이차전지 제조업</t>
+          <t>자동차부품</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>해상 운송업</t>
+          <t>해운사</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>전자장비와기기</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>생명보험</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>생명보험</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>전기장비</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>전자장비와기기</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>전자장비와기기</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>전기장비</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>전기장비</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>생명보험</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -6056,6 +6056,563 @@
         </is>
       </c>
       <c r="M111" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>5930</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>14652390</v>
+      </c>
+      <c r="E112" t="n">
+        <v>261000</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3824273.79</v>
+      </c>
+      <c r="G112" t="n">
+        <v>86</v>
+      </c>
+      <c r="H112" t="n">
+        <v>272.33</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>130</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>500</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1362361</v>
+      </c>
+      <c r="E113" t="n">
+        <v>327000</v>
+      </c>
+      <c r="F113" t="n">
+        <v>445492.047</v>
+      </c>
+      <c r="G113" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="H113" t="n">
+        <v>900.8</v>
+      </c>
+      <c r="I113" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>전기장비</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>28050</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>5474952</v>
+      </c>
+      <c r="E114" t="n">
+        <v>51800</v>
+      </c>
+      <c r="F114" t="n">
+        <v>283602.5136</v>
+      </c>
+      <c r="G114" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="H114" t="n">
+        <v>85</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>삼화콘덴서</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1645163</v>
+      </c>
+      <c r="E115" t="n">
+        <v>144600</v>
+      </c>
+      <c r="F115" t="n">
+        <v>237890.5698</v>
+      </c>
+      <c r="G115" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>340.85</v>
+      </c>
+      <c r="I115" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>55550</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>신한지주</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1549731</v>
+      </c>
+      <c r="E116" t="n">
+        <v>110100</v>
+      </c>
+      <c r="F116" t="n">
+        <v>170625.3831</v>
+      </c>
+      <c r="G116" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="H116" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="I116" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>은행</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>6340</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>대원전선</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11460689</v>
+      </c>
+      <c r="E117" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F117" t="n">
+        <v>159188.97021</v>
+      </c>
+      <c r="G117" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>395.19</v>
+      </c>
+      <c r="I117" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>전기장비</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>6360</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3129248</v>
+      </c>
+      <c r="E118" t="n">
+        <v>36850</v>
+      </c>
+      <c r="F118" t="n">
+        <v>115312.7888</v>
+      </c>
+      <c r="G118" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H118" t="n">
+        <v>92.23</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>119850</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1454036</v>
+      </c>
+      <c r="E119" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F119" t="n">
+        <v>78808.7512</v>
+      </c>
+      <c r="G119" t="n">
+        <v>51</v>
+      </c>
+      <c r="H119" t="n">
+        <v>74</v>
+      </c>
+      <c r="I119" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>전기장비</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>419708</v>
+      </c>
+      <c r="E120" t="n">
+        <v>125700</v>
+      </c>
+      <c r="F120" t="n">
+        <v>52757.2956</v>
+      </c>
+      <c r="G120" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H120" t="n">
+        <v>405.84</v>
+      </c>
+      <c r="I120" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>51</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2990</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>3123914</v>
+      </c>
+      <c r="E121" t="n">
+        <v>13340</v>
+      </c>
+      <c r="F121" t="n">
+        <v>41673.01276</v>
+      </c>
+      <c r="G121" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>226.96</v>
+      </c>
+      <c r="I121" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>672705</v>
+      </c>
+      <c r="E122" t="n">
+        <v>48800</v>
+      </c>
+      <c r="F122" t="n">
+        <v>32828.004</v>
+      </c>
+      <c r="G122" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="H122" t="n">
+        <v>76.48999999999999</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>손해보험</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t>금융</t>
         </is>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6618,6 +6618,361 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>5930</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>21530035</v>
+      </c>
+      <c r="E123" t="n">
+        <v>274000</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5899229.59</v>
+      </c>
+      <c r="G123" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="H123" t="n">
+        <v>283.22</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>130</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>4037038</v>
+      </c>
+      <c r="E124" t="n">
+        <v>208000</v>
+      </c>
+      <c r="F124" t="n">
+        <v>839703.904</v>
+      </c>
+      <c r="G124" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="H124" t="n">
+        <v>256.16</v>
+      </c>
+      <c r="I124" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>삼화콘덴서</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1154917</v>
+      </c>
+      <c r="E125" t="n">
+        <v>146000</v>
+      </c>
+      <c r="F125" t="n">
+        <v>168617.882</v>
+      </c>
+      <c r="G125" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="H125" t="n">
+        <v>345.12</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>333239</v>
+      </c>
+      <c r="E126" t="n">
+        <v>153900</v>
+      </c>
+      <c r="F126" t="n">
+        <v>51285.4821</v>
+      </c>
+      <c r="G126" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="H126" t="n">
+        <v>157.79</v>
+      </c>
+      <c r="I126" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>387266</v>
+      </c>
+      <c r="E127" t="n">
+        <v>130700</v>
+      </c>
+      <c r="F127" t="n">
+        <v>50615.6662</v>
+      </c>
+      <c r="G127" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="H127" t="n">
+        <v>361.02</v>
+      </c>
+      <c r="I127" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>51</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>144960</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>3000308</v>
+      </c>
+      <c r="E128" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F128" t="n">
+        <v>36003.696</v>
+      </c>
+      <c r="G128" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H128" t="n">
+        <v>130.77</v>
+      </c>
+      <c r="I128" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>119419</v>
+      </c>
+      <c r="E129" t="n">
+        <v>269500</v>
+      </c>
+      <c r="F129" t="n">
+        <v>32183.4205</v>
+      </c>
+      <c r="G129" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="H129" t="n">
+        <v>574.59</v>
+      </c>
+      <c r="I129" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6973,6 +6973,463 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>5930</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>16837117</v>
+      </c>
+      <c r="E130" t="n">
+        <v>276500</v>
+      </c>
+      <c r="F130" t="n">
+        <v>4655462.8505</v>
+      </c>
+      <c r="G130" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="H130" t="n">
+        <v>280.85</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>130</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>4937699</v>
+      </c>
+      <c r="E131" t="n">
+        <v>211500</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1044323.3385</v>
+      </c>
+      <c r="G131" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="H131" t="n">
+        <v>257.26</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1814102</v>
+      </c>
+      <c r="E132" t="n">
+        <v>148100</v>
+      </c>
+      <c r="F132" t="n">
+        <v>268668.5062</v>
+      </c>
+      <c r="G132" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="H132" t="n">
+        <v>416.93</v>
+      </c>
+      <c r="I132" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>51</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>삼화콘덴서</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1361490</v>
+      </c>
+      <c r="E133" t="n">
+        <v>147400</v>
+      </c>
+      <c r="F133" t="n">
+        <v>200683.626</v>
+      </c>
+      <c r="G133" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="H133" t="n">
+        <v>356.35</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>6340</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>대원전선</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>7170940</v>
+      </c>
+      <c r="E134" t="n">
+        <v>13660</v>
+      </c>
+      <c r="F134" t="n">
+        <v>97955.0404</v>
+      </c>
+      <c r="G134" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="H134" t="n">
+        <v>371.03</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>전기장비</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>429734</v>
+      </c>
+      <c r="E135" t="n">
+        <v>154300</v>
+      </c>
+      <c r="F135" t="n">
+        <v>66307.9562</v>
+      </c>
+      <c r="G135" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="H135" t="n">
+        <v>157.17</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>538980</v>
+      </c>
+      <c r="E136" t="n">
+        <v>110600</v>
+      </c>
+      <c r="F136" t="n">
+        <v>59611.188</v>
+      </c>
+      <c r="G136" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="H136" t="n">
+        <v>138.62</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>260974</v>
+      </c>
+      <c r="E137" t="n">
+        <v>146100</v>
+      </c>
+      <c r="F137" t="n">
+        <v>38128.3014</v>
+      </c>
+      <c r="G137" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>86.34999999999999</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>64290</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>682654</v>
+      </c>
+      <c r="E138" t="n">
+        <v>55600</v>
+      </c>
+      <c r="F138" t="n">
+        <v>37955.5624</v>
+      </c>
+      <c r="G138" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>282.13</v>
+      </c>
+      <c r="I138" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>-64.40000000000001</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7430,6 +7430,463 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>5930</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>18598186</v>
+      </c>
+      <c r="E139" t="n">
+        <v>285500</v>
+      </c>
+      <c r="F139" t="n">
+        <v>5309782.103</v>
+      </c>
+      <c r="G139" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>288.96</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>130</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>5161691</v>
+      </c>
+      <c r="E140" t="n">
+        <v>220000</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1135572.02</v>
+      </c>
+      <c r="G140" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="H140" t="n">
+        <v>270.99</v>
+      </c>
+      <c r="I140" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>319660</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>548944</v>
+      </c>
+      <c r="E141" t="n">
+        <v>144800</v>
+      </c>
+      <c r="F141" t="n">
+        <v>79487.0912</v>
+      </c>
+      <c r="G141" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>463.42</v>
+      </c>
+      <c r="I141" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>6360</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>2277297</v>
+      </c>
+      <c r="E142" t="n">
+        <v>34600</v>
+      </c>
+      <c r="F142" t="n">
+        <v>78794.4762</v>
+      </c>
+      <c r="G142" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H142" t="n">
+        <v>79.27</v>
+      </c>
+      <c r="I142" t="n">
+        <v>-7.73</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>95610</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>357854</v>
+      </c>
+      <c r="E143" t="n">
+        <v>161900</v>
+      </c>
+      <c r="F143" t="n">
+        <v>57936.5626</v>
+      </c>
+      <c r="G143" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>389.12</v>
+      </c>
+      <c r="I143" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>371425</v>
+      </c>
+      <c r="E144" t="n">
+        <v>155600</v>
+      </c>
+      <c r="F144" t="n">
+        <v>57793.73</v>
+      </c>
+      <c r="G144" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H144" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>270676</v>
+      </c>
+      <c r="E145" t="n">
+        <v>147000</v>
+      </c>
+      <c r="F145" t="n">
+        <v>39789.372</v>
+      </c>
+      <c r="G145" t="n">
+        <v>53</v>
+      </c>
+      <c r="H145" t="n">
+        <v>86.08</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>446540</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>3446011</v>
+      </c>
+      <c r="E146" t="n">
+        <v>10900</v>
+      </c>
+      <c r="F146" t="n">
+        <v>37561.5199</v>
+      </c>
+      <c r="G146" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="H146" t="n">
+        <v>175.95</v>
+      </c>
+      <c r="I146" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>417840</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>저스템</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1906634</v>
+      </c>
+      <c r="E147" t="n">
+        <v>17080</v>
+      </c>
+      <c r="F147" t="n">
+        <v>32565.30872</v>
+      </c>
+      <c r="G147" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="H147" t="n">
+        <v>274.07</v>
+      </c>
+      <c r="I147" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7887,6 +7887,514 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>5930</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>19385053</v>
+      </c>
+      <c r="E148" t="n">
+        <v>286500</v>
+      </c>
+      <c r="F148" t="n">
+        <v>5553817.6845</v>
+      </c>
+      <c r="G148" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="H148" t="n">
+        <v>290.33</v>
+      </c>
+      <c r="I148" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>130</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>5763244</v>
+      </c>
+      <c r="E149" t="n">
+        <v>222000</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1279440.168</v>
+      </c>
+      <c r="G149" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H149" t="n">
+        <v>274.37</v>
+      </c>
+      <c r="I149" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>36930</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>873557</v>
+      </c>
+      <c r="E150" t="n">
+        <v>209500</v>
+      </c>
+      <c r="F150" t="n">
+        <v>183010.1915</v>
+      </c>
+      <c r="G150" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="H150" t="n">
+        <v>628.7</v>
+      </c>
+      <c r="I150" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>6360</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2377160</v>
+      </c>
+      <c r="E151" t="n">
+        <v>34750</v>
+      </c>
+      <c r="F151" t="n">
+        <v>82606.31</v>
+      </c>
+      <c r="G151" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="H151" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>319660</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>561095</v>
+      </c>
+      <c r="E152" t="n">
+        <v>144200</v>
+      </c>
+      <c r="F152" t="n">
+        <v>80909.899</v>
+      </c>
+      <c r="G152" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="H152" t="n">
+        <v>461.09</v>
+      </c>
+      <c r="I152" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>376025</v>
+      </c>
+      <c r="E153" t="n">
+        <v>156500</v>
+      </c>
+      <c r="F153" t="n">
+        <v>58847.9125</v>
+      </c>
+      <c r="G153" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="H153" t="n">
+        <v>156.98</v>
+      </c>
+      <c r="I153" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>95610</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>358301</v>
+      </c>
+      <c r="E154" t="n">
+        <v>161900</v>
+      </c>
+      <c r="F154" t="n">
+        <v>58008.9319</v>
+      </c>
+      <c r="G154" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="H154" t="n">
+        <v>389.12</v>
+      </c>
+      <c r="I154" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>274025</v>
+      </c>
+      <c r="E155" t="n">
+        <v>146700</v>
+      </c>
+      <c r="F155" t="n">
+        <v>40199.4675</v>
+      </c>
+      <c r="G155" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H155" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>446540</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>3520445</v>
+      </c>
+      <c r="E156" t="n">
+        <v>10890</v>
+      </c>
+      <c r="F156" t="n">
+        <v>38337.64605</v>
+      </c>
+      <c r="G156" t="n">
+        <v>72</v>
+      </c>
+      <c r="H156" t="n">
+        <v>175.7</v>
+      </c>
+      <c r="I156" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>417840</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>저스템</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1983085</v>
+      </c>
+      <c r="E157" t="n">
+        <v>17230</v>
+      </c>
+      <c r="F157" t="n">
+        <v>34168.55455</v>
+      </c>
+      <c r="G157" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="H157" t="n">
+        <v>277.35</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,7 +1450,6 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>O</t>
@@ -1499,7 +1498,6 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>O</t>
@@ -1548,7 +1546,6 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>O</t>
@@ -1699,7 +1696,6 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>O</t>
@@ -1799,7 +1795,6 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>O</t>
@@ -2103,7 +2098,6 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>O</t>
@@ -2356,7 +2350,6 @@
           <t>손해보험</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>O</t>
@@ -2966,7 +2959,6 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>-</t>
@@ -3117,7 +3109,6 @@
           <t>손해보험</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>O</t>
@@ -3472,7 +3463,6 @@
           <t>손해보험</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>O</t>
@@ -3725,7 +3715,6 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>-</t>
@@ -4386,7 +4375,6 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>O</t>
@@ -4537,7 +4525,6 @@
           <t>생명보험</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>O</t>
@@ -4586,7 +4573,6 @@
           <t>손해보험</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>O</t>
@@ -4737,7 +4723,6 @@
           <t>생명보험</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>O</t>
@@ -4786,7 +4771,6 @@
           <t>손해보험</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>O</t>
@@ -4937,7 +4921,6 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>-</t>
@@ -5292,7 +5275,6 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>-</t>
@@ -5494,7 +5476,6 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>O</t>
@@ -5798,7 +5779,6 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>-</t>
@@ -5847,7 +5827,6 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>-</t>
@@ -6049,7 +6028,6 @@
           <t>생명보험</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>O</t>
@@ -6302,7 +6280,6 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>O</t>
@@ -6606,7 +6583,6 @@
           <t>손해보험</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>O</t>
@@ -6706,7 +6682,6 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>-</t>
@@ -7061,7 +7036,6 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>-</t>
@@ -7518,7 +7492,6 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>-</t>
@@ -7882,514 +7855,6 @@
         </is>
       </c>
       <c r="M147" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>5930</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>19385053</v>
-      </c>
-      <c r="E148" t="n">
-        <v>286500</v>
-      </c>
-      <c r="F148" t="n">
-        <v>5553817.6845</v>
-      </c>
-      <c r="G148" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="H148" t="n">
-        <v>290.33</v>
-      </c>
-      <c r="I148" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
-      <c r="K148" t="n">
-        <v>130</v>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>5935</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>5763244</v>
-      </c>
-      <c r="E149" t="n">
-        <v>222000</v>
-      </c>
-      <c r="F149" t="n">
-        <v>1279440.168</v>
-      </c>
-      <c r="G149" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="H149" t="n">
-        <v>274.37</v>
-      </c>
-      <c r="I149" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>36930</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>주성엔지니어링</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>873557</v>
-      </c>
-      <c r="E150" t="n">
-        <v>209500</v>
-      </c>
-      <c r="F150" t="n">
-        <v>183010.1915</v>
-      </c>
-      <c r="G150" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="H150" t="n">
-        <v>628.7</v>
-      </c>
-      <c r="I150" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
-      <c r="K150" t="n">
-        <v>-24</v>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>6360</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>GS건설</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>2377160</v>
-      </c>
-      <c r="E151" t="n">
-        <v>34750</v>
-      </c>
-      <c r="F151" t="n">
-        <v>82606.31</v>
-      </c>
-      <c r="G151" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="H151" t="n">
-        <v>80.05</v>
-      </c>
-      <c r="I151" t="n">
-        <v>-7.33</v>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="K151" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>319660</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>561095</v>
-      </c>
-      <c r="E152" t="n">
-        <v>144200</v>
-      </c>
-      <c r="F152" t="n">
-        <v>80909.899</v>
-      </c>
-      <c r="G152" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="H152" t="n">
-        <v>461.09</v>
-      </c>
-      <c r="I152" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
-      <c r="K152" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>10950</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>S-Oil</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>376025</v>
-      </c>
-      <c r="E153" t="n">
-        <v>156500</v>
-      </c>
-      <c r="F153" t="n">
-        <v>58847.9125</v>
-      </c>
-      <c r="G153" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="H153" t="n">
-        <v>156.98</v>
-      </c>
-      <c r="I153" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>석유와가스</t>
-        </is>
-      </c>
-      <c r="K153" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>95610</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>테스</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>358301</v>
-      </c>
-      <c r="E154" t="n">
-        <v>161900</v>
-      </c>
-      <c r="F154" t="n">
-        <v>58008.9319</v>
-      </c>
-      <c r="G154" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="H154" t="n">
-        <v>389.12</v>
-      </c>
-      <c r="I154" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
-      <c r="K154" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>161890</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>한국콜마</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>274025</v>
-      </c>
-      <c r="E155" t="n">
-        <v>146700</v>
-      </c>
-      <c r="F155" t="n">
-        <v>40199.4675</v>
-      </c>
-      <c r="G155" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H155" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>화장품</t>
-        </is>
-      </c>
-      <c r="K155" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>446540</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>메가터치</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>3520445</v>
-      </c>
-      <c r="E156" t="n">
-        <v>10890</v>
-      </c>
-      <c r="F156" t="n">
-        <v>38337.64605</v>
-      </c>
-      <c r="G156" t="n">
-        <v>72</v>
-      </c>
-      <c r="H156" t="n">
-        <v>175.7</v>
-      </c>
-      <c r="I156" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>전자장비와기기</t>
-        </is>
-      </c>
-      <c r="K156" t="n">
-        <v>107.7</v>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>417840</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>저스템</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>1983085</v>
-      </c>
-      <c r="E157" t="n">
-        <v>17230</v>
-      </c>
-      <c r="F157" t="n">
-        <v>34168.55455</v>
-      </c>
-      <c r="G157" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="H157" t="n">
-        <v>277.35</v>
-      </c>
-      <c r="I157" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
-      <c r="K157" t="n">
-        <v>159.4</v>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
         <is>
           <t>O</t>
         </is>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,6 +1450,7 @@
           <t>은행</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>O</t>
@@ -1498,6 +1499,7 @@
           <t>은행</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>O</t>
@@ -1546,6 +1548,7 @@
           <t>은행</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>O</t>
@@ -1696,6 +1699,7 @@
           <t>은행</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>O</t>
@@ -1795,6 +1799,7 @@
           <t>은행</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>O</t>
@@ -2098,6 +2103,7 @@
           <t>은행</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>O</t>
@@ -2350,6 +2356,7 @@
           <t>손해보험</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>O</t>
@@ -2959,6 +2966,7 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>-</t>
@@ -3109,6 +3117,7 @@
           <t>손해보험</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>O</t>
@@ -3463,6 +3472,7 @@
           <t>손해보험</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>O</t>
@@ -3715,6 +3725,7 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>-</t>
@@ -4375,6 +4386,7 @@
           <t>은행</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>O</t>
@@ -4525,6 +4537,7 @@
           <t>생명보험</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>O</t>
@@ -4573,6 +4586,7 @@
           <t>손해보험</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>O</t>
@@ -4723,6 +4737,7 @@
           <t>생명보험</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>O</t>
@@ -4771,6 +4786,7 @@
           <t>손해보험</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>O</t>
@@ -4921,6 +4937,7 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>-</t>
@@ -5275,6 +5292,7 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>-</t>
@@ -5476,6 +5494,7 @@
           <t>은행</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>O</t>
@@ -5779,6 +5798,7 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>-</t>
@@ -5827,6 +5847,7 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>-</t>
@@ -6028,6 +6049,7 @@
           <t>생명보험</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>O</t>
@@ -6280,6 +6302,7 @@
           <t>은행</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>O</t>
@@ -6583,6 +6606,7 @@
           <t>손해보험</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>O</t>
@@ -6682,6 +6706,7 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>-</t>
@@ -7036,6 +7061,7 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>-</t>
@@ -7492,6 +7518,7 @@
           <t>반도체와반도체장비</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>-</t>
@@ -7855,6 +7882,259 @@
         </is>
       </c>
       <c r="M147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>5930</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>20243049</v>
+      </c>
+      <c r="E148" t="n">
+        <v>270000</v>
+      </c>
+      <c r="F148" t="n">
+        <v>5465623.23</v>
+      </c>
+      <c r="G148" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="H148" t="n">
+        <v>258.09</v>
+      </c>
+      <c r="I148" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>130</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>6066334</v>
+      </c>
+      <c r="E149" t="n">
+        <v>207000</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1255731.138</v>
+      </c>
+      <c r="G149" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H149" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I149" t="n">
+        <v>-6.76</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>34730</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>153805</v>
+      </c>
+      <c r="E150" t="n">
+        <v>578000</v>
+      </c>
+      <c r="F150" t="n">
+        <v>88899.28999999999</v>
+      </c>
+      <c r="G150" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="H150" t="n">
+        <v>159.78</v>
+      </c>
+      <c r="I150" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>398774</v>
+      </c>
+      <c r="E151" t="n">
+        <v>162200</v>
+      </c>
+      <c r="F151" t="n">
+        <v>64681.1428</v>
+      </c>
+      <c r="G151" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="H151" t="n">
+        <v>173.99</v>
+      </c>
+      <c r="I151" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>405206</v>
+      </c>
+      <c r="E152" t="n">
+        <v>113800</v>
+      </c>
+      <c r="F152" t="n">
+        <v>46112.4428</v>
+      </c>
+      <c r="G152" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="H152" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I152" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t>O</t>
         </is>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8140,6 +8140,261 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>36930</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>990532</v>
+      </c>
+      <c r="E153" t="n">
+        <v>222000</v>
+      </c>
+      <c r="F153" t="n">
+        <v>219898.104</v>
+      </c>
+      <c r="G153" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="H153" t="n">
+        <v>646.22</v>
+      </c>
+      <c r="I153" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>삼화콘덴서</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1354754</v>
+      </c>
+      <c r="E154" t="n">
+        <v>157500</v>
+      </c>
+      <c r="F154" t="n">
+        <v>213373.755</v>
+      </c>
+      <c r="G154" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="H154" t="n">
+        <v>386.86</v>
+      </c>
+      <c r="I154" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>95610</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>345850</v>
+      </c>
+      <c r="E155" t="n">
+        <v>170800</v>
+      </c>
+      <c r="F155" t="n">
+        <v>59071.18</v>
+      </c>
+      <c r="G155" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H155" t="n">
+        <v>312.06</v>
+      </c>
+      <c r="I155" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>115909</v>
+      </c>
+      <c r="E156" t="n">
+        <v>297000</v>
+      </c>
+      <c r="F156" t="n">
+        <v>34424.973</v>
+      </c>
+      <c r="G156" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="H156" t="n">
+        <v>544.95</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>187790</v>
+      </c>
+      <c r="E157" t="n">
+        <v>180800</v>
+      </c>
+      <c r="F157" t="n">
+        <v>33952.432</v>
+      </c>
+      <c r="G157" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H157" t="n">
+        <v>350.87</v>
+      </c>
+      <c r="I157" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8395,6 +8395,261 @@
         </is>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>36930</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1231672</v>
+      </c>
+      <c r="E158" t="n">
+        <v>232500</v>
+      </c>
+      <c r="F158" t="n">
+        <v>286363.74</v>
+      </c>
+      <c r="G158" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="H158" t="n">
+        <v>668.6</v>
+      </c>
+      <c r="I158" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>34730</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>153369</v>
+      </c>
+      <c r="E159" t="n">
+        <v>588000</v>
+      </c>
+      <c r="F159" t="n">
+        <v>90180.97199999999</v>
+      </c>
+      <c r="G159" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="H159" t="n">
+        <v>152.36</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>95610</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>278433</v>
+      </c>
+      <c r="E160" t="n">
+        <v>167700</v>
+      </c>
+      <c r="F160" t="n">
+        <v>46693.2141</v>
+      </c>
+      <c r="G160" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="H160" t="n">
+        <v>303.61</v>
+      </c>
+      <c r="I160" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>264472</v>
+      </c>
+      <c r="E161" t="n">
+        <v>146000</v>
+      </c>
+      <c r="F161" t="n">
+        <v>38612.912</v>
+      </c>
+      <c r="G161" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="H161" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="I161" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>417840</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>저스템</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1740347</v>
+      </c>
+      <c r="E162" t="n">
+        <v>18570</v>
+      </c>
+      <c r="F162" t="n">
+        <v>32318.24379</v>
+      </c>
+      <c r="G162" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="H162" t="n">
+        <v>314.69</v>
+      </c>
+      <c r="I162" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8650,6 +8650,414 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>36930</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1550825</v>
+      </c>
+      <c r="E163" t="n">
+        <v>241000</v>
+      </c>
+      <c r="F163" t="n">
+        <v>373748.825</v>
+      </c>
+      <c r="G163" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="H163" t="n">
+        <v>706.02</v>
+      </c>
+      <c r="I163" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>삼화콘덴서</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1212784</v>
+      </c>
+      <c r="E164" t="n">
+        <v>158700</v>
+      </c>
+      <c r="F164" t="n">
+        <v>192468.8208</v>
+      </c>
+      <c r="G164" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="H164" t="n">
+        <v>400.63</v>
+      </c>
+      <c r="I164" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>93370</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>후성</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>8502014</v>
+      </c>
+      <c r="E165" t="n">
+        <v>15710</v>
+      </c>
+      <c r="F165" t="n">
+        <v>133566.63994</v>
+      </c>
+      <c r="G165" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="H165" t="n">
+        <v>153.8</v>
+      </c>
+      <c r="I165" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>764434</v>
+      </c>
+      <c r="E166" t="n">
+        <v>159700</v>
+      </c>
+      <c r="F166" t="n">
+        <v>122080.1098</v>
+      </c>
+      <c r="G166" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H166" t="n">
+        <v>390.63</v>
+      </c>
+      <c r="I166" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>51</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>95610</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>406283</v>
+      </c>
+      <c r="E167" t="n">
+        <v>183900</v>
+      </c>
+      <c r="F167" t="n">
+        <v>74715.4437</v>
+      </c>
+      <c r="G167" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="H167" t="n">
+        <v>343.13</v>
+      </c>
+      <c r="I167" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>406117</v>
+      </c>
+      <c r="E168" t="n">
+        <v>148800</v>
+      </c>
+      <c r="F168" t="n">
+        <v>60430.2096</v>
+      </c>
+      <c r="G168" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H168" t="n">
+        <v>153.06</v>
+      </c>
+      <c r="I168" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>319660</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>371124</v>
+      </c>
+      <c r="E169" t="n">
+        <v>161900</v>
+      </c>
+      <c r="F169" t="n">
+        <v>60084.9756</v>
+      </c>
+      <c r="G169" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="H169" t="n">
+        <v>478.21</v>
+      </c>
+      <c r="I169" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>216144</v>
+      </c>
+      <c r="E170" t="n">
+        <v>194000</v>
+      </c>
+      <c r="F170" t="n">
+        <v>41931.936</v>
+      </c>
+      <c r="G170" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="H170" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="I170" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9058,6 +9058,465 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>80220</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>4152258</v>
+      </c>
+      <c r="E171" t="n">
+        <v>92400</v>
+      </c>
+      <c r="F171" t="n">
+        <v>383668.6392</v>
+      </c>
+      <c r="G171" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H171" t="n">
+        <v>383.01</v>
+      </c>
+      <c r="I171" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
+        <v>467.8</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>36930</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1279946</v>
+      </c>
+      <c r="E172" t="n">
+        <v>237000</v>
+      </c>
+      <c r="F172" t="n">
+        <v>303347.202</v>
+      </c>
+      <c r="G172" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="H172" t="n">
+        <v>665.75</v>
+      </c>
+      <c r="I172" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1049167</v>
+      </c>
+      <c r="E173" t="n">
+        <v>167200</v>
+      </c>
+      <c r="F173" t="n">
+        <v>175420.7224</v>
+      </c>
+      <c r="G173" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="H173" t="n">
+        <v>405.14</v>
+      </c>
+      <c r="I173" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K173" t="n">
+        <v>51</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>327260</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1947068</v>
+      </c>
+      <c r="E174" t="n">
+        <v>52500</v>
+      </c>
+      <c r="F174" t="n">
+        <v>102221.07</v>
+      </c>
+      <c r="G174" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="H174" t="n">
+        <v>733.0700000000001</v>
+      </c>
+      <c r="I174" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>우주항공과국방</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>451419</v>
+      </c>
+      <c r="E175" t="n">
+        <v>166200</v>
+      </c>
+      <c r="F175" t="n">
+        <v>75025.83779999999</v>
+      </c>
+      <c r="G175" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="H175" t="n">
+        <v>183.13</v>
+      </c>
+      <c r="I175" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>319660</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>466441</v>
+      </c>
+      <c r="E176" t="n">
+        <v>152000</v>
+      </c>
+      <c r="F176" t="n">
+        <v>70899.03200000001</v>
+      </c>
+      <c r="G176" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="H176" t="n">
+        <v>420.55</v>
+      </c>
+      <c r="I176" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>500</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>187241</v>
+      </c>
+      <c r="E177" t="n">
+        <v>329000</v>
+      </c>
+      <c r="F177" t="n">
+        <v>61602.289</v>
+      </c>
+      <c r="G177" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="H177" t="n">
+        <v>893.42</v>
+      </c>
+      <c r="I177" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>전기장비</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>199865</v>
+      </c>
+      <c r="E178" t="n">
+        <v>193600</v>
+      </c>
+      <c r="F178" t="n">
+        <v>38693.864</v>
+      </c>
+      <c r="G178" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="H178" t="n">
+        <v>336.53</v>
+      </c>
+      <c r="I178" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>115896</v>
+      </c>
+      <c r="E179" t="n">
+        <v>290500</v>
+      </c>
+      <c r="F179" t="n">
+        <v>33667.788</v>
+      </c>
+      <c r="G179" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H179" t="n">
+        <v>525.4</v>
+      </c>
+      <c r="I179" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M179"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9517,6 +9517,567 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>9150</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>727497</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1218557.475</v>
+      </c>
+      <c r="G180" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="H180" t="n">
+        <v>747.24</v>
+      </c>
+      <c r="I180" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>36930</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>3188639</v>
+      </c>
+      <c r="E181" t="n">
+        <v>278500</v>
+      </c>
+      <c r="F181" t="n">
+        <v>888035.9615</v>
+      </c>
+      <c r="G181" t="n">
+        <v>97</v>
+      </c>
+      <c r="H181" t="n">
+        <v>759.5700000000001</v>
+      </c>
+      <c r="I181" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>930476</v>
+      </c>
+      <c r="E182" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F182" t="n">
+        <v>162833.3</v>
+      </c>
+      <c r="G182" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="H182" t="n">
+        <v>422.39</v>
+      </c>
+      <c r="I182" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>51</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>356680</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>엑스게이트</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>7002276</v>
+      </c>
+      <c r="E183" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F183" t="n">
+        <v>143546.658</v>
+      </c>
+      <c r="G183" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="H183" t="n">
+        <v>146.39</v>
+      </c>
+      <c r="I183" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>34730</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>119076</v>
+      </c>
+      <c r="E184" t="n">
+        <v>586000</v>
+      </c>
+      <c r="F184" t="n">
+        <v>69778.53599999999</v>
+      </c>
+      <c r="G184" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="H184" t="n">
+        <v>158.15</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>388958</v>
+      </c>
+      <c r="E185" t="n">
+        <v>165300</v>
+      </c>
+      <c r="F185" t="n">
+        <v>64294.7574</v>
+      </c>
+      <c r="G185" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="H185" t="n">
+        <v>185.99</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>360413</v>
+      </c>
+      <c r="E186" t="n">
+        <v>138900</v>
+      </c>
+      <c r="F186" t="n">
+        <v>50061.3657</v>
+      </c>
+      <c r="G186" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="H186" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>500</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>137046</v>
+      </c>
+      <c r="E187" t="n">
+        <v>327000</v>
+      </c>
+      <c r="F187" t="n">
+        <v>44814.042</v>
+      </c>
+      <c r="G187" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="H187" t="n">
+        <v>899.11</v>
+      </c>
+      <c r="I187" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>전기장비</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>210185</v>
+      </c>
+      <c r="E188" t="n">
+        <v>197000</v>
+      </c>
+      <c r="F188" t="n">
+        <v>41406.445</v>
+      </c>
+      <c r="G188" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="H188" t="n">
+        <v>329.19</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>281820</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>케이씨텍</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>369282</v>
+      </c>
+      <c r="E189" t="n">
+        <v>107400</v>
+      </c>
+      <c r="F189" t="n">
+        <v>39660.8868</v>
+      </c>
+      <c r="G189" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="H189" t="n">
+        <v>177.88</v>
+      </c>
+      <c r="I189" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>100194</v>
+      </c>
+      <c r="E190" t="n">
+        <v>313500</v>
+      </c>
+      <c r="F190" t="n">
+        <v>31410.819</v>
+      </c>
+      <c r="G190" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H190" t="n">
+        <v>566.3099999999999</v>
+      </c>
+      <c r="I190" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10078,6 +10078,465 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>5930</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>15933455</v>
+      </c>
+      <c r="E191" t="n">
+        <v>268500</v>
+      </c>
+      <c r="F191" t="n">
+        <v>4278132.6675</v>
+      </c>
+      <c r="G191" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="H191" t="n">
+        <v>221.56</v>
+      </c>
+      <c r="I191" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
+        <v>130</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>36930</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>2170537</v>
+      </c>
+      <c r="E192" t="n">
+        <v>247500</v>
+      </c>
+      <c r="F192" t="n">
+        <v>537207.9075</v>
+      </c>
+      <c r="G192" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="H192" t="n">
+        <v>665.0700000000001</v>
+      </c>
+      <c r="I192" t="n">
+        <v>-12.54</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>500</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>485645</v>
+      </c>
+      <c r="E193" t="n">
+        <v>306500</v>
+      </c>
+      <c r="F193" t="n">
+        <v>148850.1925</v>
+      </c>
+      <c r="G193" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="H193" t="n">
+        <v>830.14</v>
+      </c>
+      <c r="I193" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>전기장비</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>281820</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>케이씨텍</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1086457</v>
+      </c>
+      <c r="E194" t="n">
+        <v>123000</v>
+      </c>
+      <c r="F194" t="n">
+        <v>133634.211</v>
+      </c>
+      <c r="G194" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="H194" t="n">
+        <v>214.18</v>
+      </c>
+      <c r="I194" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>257455</v>
+      </c>
+      <c r="E195" t="n">
+        <v>316000</v>
+      </c>
+      <c r="F195" t="n">
+        <v>81355.78</v>
+      </c>
+      <c r="G195" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="H195" t="n">
+        <v>554.92</v>
+      </c>
+      <c r="I195" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>501018</v>
+      </c>
+      <c r="E196" t="n">
+        <v>145600</v>
+      </c>
+      <c r="F196" t="n">
+        <v>72948.2208</v>
+      </c>
+      <c r="G196" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="H196" t="n">
+        <v>80.42</v>
+      </c>
+      <c r="I196" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>95610</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>398122</v>
+      </c>
+      <c r="E197" t="n">
+        <v>163100</v>
+      </c>
+      <c r="F197" t="n">
+        <v>64933.6982</v>
+      </c>
+      <c r="G197" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="H197" t="n">
+        <v>271.95</v>
+      </c>
+      <c r="I197" t="n">
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>453366</v>
+      </c>
+      <c r="E198" t="n">
+        <v>109900</v>
+      </c>
+      <c r="F198" t="n">
+        <v>49824.9234</v>
+      </c>
+      <c r="G198" t="n">
+        <v>64</v>
+      </c>
+      <c r="H198" t="n">
+        <v>138.39</v>
+      </c>
+      <c r="I198" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>239559</v>
+      </c>
+      <c r="E199" t="n">
+        <v>204000</v>
+      </c>
+      <c r="F199" t="n">
+        <v>48870.036</v>
+      </c>
+      <c r="G199" t="n">
+        <v>88</v>
+      </c>
+      <c r="H199" t="n">
+        <v>341.08</v>
+      </c>
+      <c r="I199" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K199" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M199"/>
+  <dimension ref="A1:M205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10537,6 +10537,312 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>5930</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>19540404</v>
+      </c>
+      <c r="E200" t="n">
+        <v>262000</v>
+      </c>
+      <c r="F200" t="n">
+        <v>5119585.848</v>
+      </c>
+      <c r="G200" t="n">
+        <v>83</v>
+      </c>
+      <c r="H200" t="n">
+        <v>209.33</v>
+      </c>
+      <c r="I200" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K200" t="n">
+        <v>130</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>36930</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>3696842</v>
+      </c>
+      <c r="E201" t="n">
+        <v>267500</v>
+      </c>
+      <c r="F201" t="n">
+        <v>988905.235</v>
+      </c>
+      <c r="G201" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="H201" t="n">
+        <v>735.9400000000001</v>
+      </c>
+      <c r="I201" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>417840</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>저스템</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>3250262</v>
+      </c>
+      <c r="E202" t="n">
+        <v>20900</v>
+      </c>
+      <c r="F202" t="n">
+        <v>67930.4758</v>
+      </c>
+      <c r="G202" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="H202" t="n">
+        <v>358.43</v>
+      </c>
+      <c r="I202" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>28050</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1369368</v>
+      </c>
+      <c r="E203" t="n">
+        <v>48250</v>
+      </c>
+      <c r="F203" t="n">
+        <v>66072.00599999999</v>
+      </c>
+      <c r="G203" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="H203" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="I203" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="K203" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>319660</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>432726</v>
+      </c>
+      <c r="E204" t="n">
+        <v>145100</v>
+      </c>
+      <c r="F204" t="n">
+        <v>62788.5426</v>
+      </c>
+      <c r="G204" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H204" t="n">
+        <v>357.73</v>
+      </c>
+      <c r="I204" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K204" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>6110</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>삼아알미늄</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>574211</v>
+      </c>
+      <c r="E205" t="n">
+        <v>74800</v>
+      </c>
+      <c r="F205" t="n">
+        <v>42950.9828</v>
+      </c>
+      <c r="G205" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="H205" t="n">
+        <v>240</v>
+      </c>
+      <c r="I205" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>비철금속</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M205"/>
+  <dimension ref="A1:M210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10843,6 +10843,261 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2990</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>14167170</v>
+      </c>
+      <c r="E206" t="n">
+        <v>13400</v>
+      </c>
+      <c r="F206" t="n">
+        <v>189840.078</v>
+      </c>
+      <c r="G206" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="H206" t="n">
+        <v>255.44</v>
+      </c>
+      <c r="I206" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>246030</v>
+      </c>
+      <c r="E207" t="n">
+        <v>308000</v>
+      </c>
+      <c r="F207" t="n">
+        <v>75777.24000000001</v>
+      </c>
+      <c r="G207" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H207" t="n">
+        <v>487.79</v>
+      </c>
+      <c r="I207" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>28670</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>9860101</v>
+      </c>
+      <c r="E208" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F208" t="n">
+        <v>63597.65145</v>
+      </c>
+      <c r="G208" t="n">
+        <v>53</v>
+      </c>
+      <c r="H208" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="I208" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>해운사</t>
+        </is>
+      </c>
+      <c r="K208" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>95610</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>386725</v>
+      </c>
+      <c r="E209" t="n">
+        <v>161800</v>
+      </c>
+      <c r="F209" t="n">
+        <v>62572.105</v>
+      </c>
+      <c r="G209" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="H209" t="n">
+        <v>254.82</v>
+      </c>
+      <c r="I209" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>267374</v>
+      </c>
+      <c r="E210" t="n">
+        <v>201500</v>
+      </c>
+      <c r="F210" t="n">
+        <v>53875.861</v>
+      </c>
+      <c r="G210" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="H210" t="n">
+        <v>311.22</v>
+      </c>
+      <c r="I210" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M210"/>
+  <dimension ref="A1:M220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11098,6 +11098,516 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>668795</v>
+      </c>
+      <c r="E211" t="n">
+        <v>560000</v>
+      </c>
+      <c r="F211" t="n">
+        <v>374525.2</v>
+      </c>
+      <c r="G211" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="H211" t="n">
+        <v>166.03</v>
+      </c>
+      <c r="I211" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1201624</v>
+      </c>
+      <c r="E212" t="n">
+        <v>150500</v>
+      </c>
+      <c r="F212" t="n">
+        <v>180844.412</v>
+      </c>
+      <c r="G212" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="H212" t="n">
+        <v>262.21</v>
+      </c>
+      <c r="I212" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K212" t="n">
+        <v>51</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>403870</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>2203445</v>
+      </c>
+      <c r="E213" t="n">
+        <v>61600</v>
+      </c>
+      <c r="F213" t="n">
+        <v>135732.212</v>
+      </c>
+      <c r="G213" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="H213" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="I213" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K213" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>319660</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>517960</v>
+      </c>
+      <c r="E214" t="n">
+        <v>149100</v>
+      </c>
+      <c r="F214" t="n">
+        <v>77227.836</v>
+      </c>
+      <c r="G214" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="H214" t="n">
+        <v>360.19</v>
+      </c>
+      <c r="I214" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>500</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>238815</v>
+      </c>
+      <c r="E215" t="n">
+        <v>279500</v>
+      </c>
+      <c r="F215" t="n">
+        <v>66748.7925</v>
+      </c>
+      <c r="G215" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="H215" t="n">
+        <v>770.23</v>
+      </c>
+      <c r="I215" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>전기장비</t>
+        </is>
+      </c>
+      <c r="K215" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>184170</v>
+      </c>
+      <c r="E216" t="n">
+        <v>329500</v>
+      </c>
+      <c r="F216" t="n">
+        <v>60684.015</v>
+      </c>
+      <c r="G216" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="H216" t="n">
+        <v>539.8099999999999</v>
+      </c>
+      <c r="I216" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K216" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>28670</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>8647002</v>
+      </c>
+      <c r="E217" t="n">
+        <v>6550</v>
+      </c>
+      <c r="F217" t="n">
+        <v>56637.8631</v>
+      </c>
+      <c r="G217" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="H217" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>해운사</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>253792</v>
+      </c>
+      <c r="E218" t="n">
+        <v>216000</v>
+      </c>
+      <c r="F218" t="n">
+        <v>54819.072</v>
+      </c>
+      <c r="G218" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="H218" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="I218" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>417840</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>저스템</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>2367986</v>
+      </c>
+      <c r="E219" t="n">
+        <v>19120</v>
+      </c>
+      <c r="F219" t="n">
+        <v>45275.89232</v>
+      </c>
+      <c r="G219" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="H219" t="n">
+        <v>326.31</v>
+      </c>
+      <c r="I219" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K219" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>327260</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>903293</v>
+      </c>
+      <c r="E220" t="n">
+        <v>49950</v>
+      </c>
+      <c r="F220" t="n">
+        <v>45119.48535</v>
+      </c>
+      <c r="G220" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="H220" t="n">
+        <v>602.83</v>
+      </c>
+      <c r="I220" t="n">
+        <v>-7.67</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>우주항공과국방</t>
+        </is>
+      </c>
+      <c r="K220" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M220"/>
+  <dimension ref="A1:M226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -631,7 +631,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>기계</t>
+          <t>기타 금속 가공제품 제조업</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -988,7 +988,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>에너지장비및서비스</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>담배</t>
+          <t>담배 제조업</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>건강관리장비와용품</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>자동차부품</t>
+          <t>일차전지 및 이차전지 제조업</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>해운사</t>
+          <t>해상 운송업</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>생명보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>생명보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>생명보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>손해보험</t>
+          <t>보험업</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K134" t="n">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K144" t="n">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>일차전지 및 이차전지 제조업</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="K148" t="n">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K153" t="n">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K154" t="n">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K158" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K159" t="n">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K160" t="n">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K161" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K163" t="n">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K164" t="n">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="K165" t="n">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K166" t="n">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K168" t="n">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K169" t="n">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K170" t="n">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="K171" t="n">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K173" t="n">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>우주항공과국방</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K174" t="n">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K175" t="n">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K176" t="n">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K178" t="n">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K179" t="n">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K180" t="n">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K181" t="n">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="K183" t="n">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K184" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>석유 정제품 제조업</t>
         </is>
       </c>
       <c r="K185" t="n">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K186" t="n">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K188" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K189" t="n">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K190" t="n">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="K191" t="n">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K193" t="n">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K194" t="n">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K195" t="n">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="K196" t="n">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>석유와가스</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="K198" t="n">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K199" t="n">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="K200" t="n">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K201" t="n">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
         </is>
       </c>
       <c r="K203" t="n">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K204" t="n">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>비철금속</t>
+          <t>1차 비철금속 제조업</t>
         </is>
       </c>
       <c r="K205" t="n">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>건물 건설업</t>
         </is>
       </c>
       <c r="K206" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>해운사</t>
+          <t>해상 운송업</t>
         </is>
       </c>
       <c r="K208" t="n">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K209" t="n">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K210" t="n">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>일차전지 및 이차전지 제조업</t>
         </is>
       </c>
       <c r="K211" t="n">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>전자장비와기기</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K213" t="n">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K214" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>전기장비</t>
+          <t>절연선 및 케이블 제조업</t>
         </is>
       </c>
       <c r="K215" t="n">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="K216" t="n">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>해운사</t>
+          <t>해상 운송업</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K218" t="n">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>반도체와반도체장비</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="K219" t="n">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>우주항공과국방</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="K220" t="n">
@@ -11603,6 +11603,312 @@
         </is>
       </c>
       <c r="M220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>852470</v>
+      </c>
+      <c r="E221" t="n">
+        <v>591000</v>
+      </c>
+      <c r="F221" t="n">
+        <v>503809.77</v>
+      </c>
+      <c r="G221" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="H221" t="n">
+        <v>191.85</v>
+      </c>
+      <c r="I221" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>일차전지 및 이차전지 제조업</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>916443</v>
+      </c>
+      <c r="E222" t="n">
+        <v>141000</v>
+      </c>
+      <c r="F222" t="n">
+        <v>129218.463</v>
+      </c>
+      <c r="G222" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="H222" t="n">
+        <v>247.29</v>
+      </c>
+      <c r="I222" t="n">
+        <v>-7.78</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>51</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>28670</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>16862118</v>
+      </c>
+      <c r="E223" t="n">
+        <v>7240</v>
+      </c>
+      <c r="F223" t="n">
+        <v>122081.73432</v>
+      </c>
+      <c r="G223" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="H223" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="I223" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>해상 운송업</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>416566</v>
+      </c>
+      <c r="E224" t="n">
+        <v>209000</v>
+      </c>
+      <c r="F224" t="n">
+        <v>87062.29399999999</v>
+      </c>
+      <c r="G224" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H224" t="n">
+        <v>364.44</v>
+      </c>
+      <c r="I224" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>327260</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>921764</v>
+      </c>
+      <c r="E225" t="n">
+        <v>47400</v>
+      </c>
+      <c r="F225" t="n">
+        <v>43691.6136</v>
+      </c>
+      <c r="G225" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="H225" t="n">
+        <v>610.33</v>
+      </c>
+      <c r="I225" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>92870</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>엑시콘</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>580041</v>
+      </c>
+      <c r="E226" t="n">
+        <v>50600</v>
+      </c>
+      <c r="F226" t="n">
+        <v>29350.0746</v>
+      </c>
+      <c r="G226" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="H226" t="n">
+        <v>258.61</v>
+      </c>
+      <c r="I226" t="n">
+        <v>-12.31</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t>O</t>
         </is>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M226"/>
+  <dimension ref="A1:M236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11914,6 +11914,516 @@
         </is>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>832854</v>
+      </c>
+      <c r="E227" t="n">
+        <v>536000</v>
+      </c>
+      <c r="F227" t="n">
+        <v>446409.744</v>
+      </c>
+      <c r="G227" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="H227" t="n">
+        <v>160.19</v>
+      </c>
+      <c r="I227" t="n">
+        <v>-10.07</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>일차전지 및 이차전지 제조업</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>96770</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1043064</v>
+      </c>
+      <c r="E228" t="n">
+        <v>153500</v>
+      </c>
+      <c r="F228" t="n">
+        <v>160110.324</v>
+      </c>
+      <c r="G228" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H228" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="I228" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>28670</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>16228296</v>
+      </c>
+      <c r="E229" t="n">
+        <v>6680</v>
+      </c>
+      <c r="F229" t="n">
+        <v>108405.01728</v>
+      </c>
+      <c r="G229" t="n">
+        <v>61</v>
+      </c>
+      <c r="H229" t="n">
+        <v>70.88</v>
+      </c>
+      <c r="I229" t="n">
+        <v>-7.61</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>해상 운송업</t>
+        </is>
+      </c>
+      <c r="K229" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>303896</v>
+      </c>
+      <c r="E230" t="n">
+        <v>187000</v>
+      </c>
+      <c r="F230" t="n">
+        <v>56828.552</v>
+      </c>
+      <c r="G230" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H230" t="n">
+        <v>306.52</v>
+      </c>
+      <c r="I230" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K230" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>330815</v>
+      </c>
+      <c r="E231" t="n">
+        <v>158500</v>
+      </c>
+      <c r="F231" t="n">
+        <v>52434.1775</v>
+      </c>
+      <c r="G231" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="H231" t="n">
+        <v>143.98</v>
+      </c>
+      <c r="I231" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K231" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>92870</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>엑시콘</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1165539</v>
+      </c>
+      <c r="E232" t="n">
+        <v>44200</v>
+      </c>
+      <c r="F232" t="n">
+        <v>51516.8238</v>
+      </c>
+      <c r="G232" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="H232" t="n">
+        <v>199.66</v>
+      </c>
+      <c r="I232" t="n">
+        <v>-12.65</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>500</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>198203</v>
+      </c>
+      <c r="E233" t="n">
+        <v>246000</v>
+      </c>
+      <c r="F233" t="n">
+        <v>48757.938</v>
+      </c>
+      <c r="G233" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="H233" t="n">
+        <v>718.3099999999999</v>
+      </c>
+      <c r="I233" t="n">
+        <v>-14.29</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>36540</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>5190839</v>
+      </c>
+      <c r="E234" t="n">
+        <v>8930</v>
+      </c>
+      <c r="F234" t="n">
+        <v>46354.19227</v>
+      </c>
+      <c r="G234" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="H234" t="n">
+        <v>125.51</v>
+      </c>
+      <c r="I234" t="n">
+        <v>-13.13</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>163864</v>
+      </c>
+      <c r="E235" t="n">
+        <v>271000</v>
+      </c>
+      <c r="F235" t="n">
+        <v>44407.144</v>
+      </c>
+      <c r="G235" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="H235" t="n">
+        <v>414.23</v>
+      </c>
+      <c r="I235" t="n">
+        <v>-15.71</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+        </is>
+      </c>
+      <c r="K235" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>64290</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>730820</v>
+      </c>
+      <c r="E236" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F236" t="n">
+        <v>36541</v>
+      </c>
+      <c r="G236" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="H236" t="n">
+        <v>172.18</v>
+      </c>
+      <c r="I236" t="n">
+        <v>-14.82</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K236" t="n">
+        <v>-64.40000000000001</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M236"/>
+  <dimension ref="A1:M243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12424,6 +12424,363 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>357359</v>
+      </c>
+      <c r="E237" t="n">
+        <v>199000</v>
+      </c>
+      <c r="F237" t="n">
+        <v>71114.44100000001</v>
+      </c>
+      <c r="G237" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="H237" t="n">
+        <v>336.88</v>
+      </c>
+      <c r="I237" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K237" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>417906</v>
+      </c>
+      <c r="E238" t="n">
+        <v>153700</v>
+      </c>
+      <c r="F238" t="n">
+        <v>64232.1522</v>
+      </c>
+      <c r="G238" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="H238" t="n">
+        <v>146.31</v>
+      </c>
+      <c r="I238" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K238" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>500</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>217275</v>
+      </c>
+      <c r="E239" t="n">
+        <v>251000</v>
+      </c>
+      <c r="F239" t="n">
+        <v>54536.025</v>
+      </c>
+      <c r="G239" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="H239" t="n">
+        <v>715.36</v>
+      </c>
+      <c r="I239" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="K239" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>36540</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>4796134</v>
+      </c>
+      <c r="E240" t="n">
+        <v>9400</v>
+      </c>
+      <c r="F240" t="n">
+        <v>45083.6596</v>
+      </c>
+      <c r="G240" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="H240" t="n">
+        <v>129.55</v>
+      </c>
+      <c r="I240" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>92870</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>엑시콘</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>787170</v>
+      </c>
+      <c r="E241" t="n">
+        <v>54100</v>
+      </c>
+      <c r="F241" t="n">
+        <v>42585.897</v>
+      </c>
+      <c r="G241" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="H241" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="I241" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K241" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>64290</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>701621</v>
+      </c>
+      <c r="E242" t="n">
+        <v>57700</v>
+      </c>
+      <c r="F242" t="n">
+        <v>40483.5317</v>
+      </c>
+      <c r="G242" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="H242" t="n">
+        <v>207.24</v>
+      </c>
+      <c r="I242" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K242" t="n">
+        <v>-64.40000000000001</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>144960</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>2946065</v>
+      </c>
+      <c r="E243" t="n">
+        <v>11930</v>
+      </c>
+      <c r="F243" t="n">
+        <v>35146.55545</v>
+      </c>
+      <c r="G243" t="n">
+        <v>72</v>
+      </c>
+      <c r="H243" t="n">
+        <v>126.38</v>
+      </c>
+      <c r="I243" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K243" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M243"/>
+  <dimension ref="A1:M246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12781,6 +12781,159 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1003956</v>
+      </c>
+      <c r="E244" t="n">
+        <v>592000</v>
+      </c>
+      <c r="F244" t="n">
+        <v>594341.952</v>
+      </c>
+      <c r="G244" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="H244" t="n">
+        <v>190.2</v>
+      </c>
+      <c r="I244" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>일차전지 및 이차전지 제조업</t>
+        </is>
+      </c>
+      <c r="K244" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>6110</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>삼아알미늄</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>495825</v>
+      </c>
+      <c r="E245" t="n">
+        <v>82100</v>
+      </c>
+      <c r="F245" t="n">
+        <v>40707.2325</v>
+      </c>
+      <c r="G245" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="H245" t="n">
+        <v>307.44</v>
+      </c>
+      <c r="I245" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>1차 비철금속 제조업</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>64290</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>538373</v>
+      </c>
+      <c r="E246" t="n">
+        <v>59300</v>
+      </c>
+      <c r="F246" t="n">
+        <v>31925.5189</v>
+      </c>
+      <c r="G246" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="H246" t="n">
+        <v>222.28</v>
+      </c>
+      <c r="I246" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K246" t="n">
+        <v>-64.40000000000001</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M246"/>
+  <dimension ref="A1:M247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12934,6 +12934,57 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>144960</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>2271692</v>
+      </c>
+      <c r="E247" t="n">
+        <v>12810</v>
+      </c>
+      <c r="F247" t="n">
+        <v>29100.37452</v>
+      </c>
+      <c r="G247" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="H247" t="n">
+        <v>110.34</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K247" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M247"/>
+  <dimension ref="A1:M251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12985,6 +12985,210 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>96770</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>854655</v>
+      </c>
+      <c r="E248" t="n">
+        <v>154300</v>
+      </c>
+      <c r="F248" t="n">
+        <v>131873.2665</v>
+      </c>
+      <c r="G248" t="n">
+        <v>56</v>
+      </c>
+      <c r="H248" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="I248" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K248" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>144960</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>3326871</v>
+      </c>
+      <c r="E249" t="n">
+        <v>13690</v>
+      </c>
+      <c r="F249" t="n">
+        <v>45544.86399</v>
+      </c>
+      <c r="G249" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="H249" t="n">
+        <v>107.11</v>
+      </c>
+      <c r="I249" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>36540</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>4554594</v>
+      </c>
+      <c r="E250" t="n">
+        <v>9450</v>
+      </c>
+      <c r="F250" t="n">
+        <v>43040.9133</v>
+      </c>
+      <c r="G250" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="H250" t="n">
+        <v>106.11</v>
+      </c>
+      <c r="I250" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="K250" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>281820</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>케이씨텍</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>309464</v>
+      </c>
+      <c r="E251" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F251" t="n">
+        <v>30946.4</v>
+      </c>
+      <c r="G251" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="H251" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="I251" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M251"/>
+  <dimension ref="A1:M253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13189,6 +13189,108 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>28050</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>11542644</v>
+      </c>
+      <c r="E252" t="n">
+        <v>55400</v>
+      </c>
+      <c r="F252" t="n">
+        <v>639462.4776</v>
+      </c>
+      <c r="G252" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="H252" t="n">
+        <v>102.19</v>
+      </c>
+      <c r="I252" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>33780</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>KT&amp;G</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>277941</v>
+      </c>
+      <c r="E253" t="n">
+        <v>193800</v>
+      </c>
+      <c r="F253" t="n">
+        <v>53864.9658</v>
+      </c>
+      <c r="G253" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="H253" t="n">
+        <v>44.63</v>
+      </c>
+      <c r="I253" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>담배 제조업</t>
+        </is>
+      </c>
+      <c r="K253" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M253"/>
+  <dimension ref="A1:M256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13291,6 +13291,159 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>28050</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>12670773</v>
+      </c>
+      <c r="E254" t="n">
+        <v>59800</v>
+      </c>
+      <c r="F254" t="n">
+        <v>757712.2254</v>
+      </c>
+      <c r="G254" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="H254" t="n">
+        <v>112.81</v>
+      </c>
+      <c r="I254" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
+        </is>
+      </c>
+      <c r="K254" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>33780</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>KT&amp;G</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>297626</v>
+      </c>
+      <c r="E255" t="n">
+        <v>189400</v>
+      </c>
+      <c r="F255" t="n">
+        <v>56370.3644</v>
+      </c>
+      <c r="G255" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="H255" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="I255" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>담배 제조업</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>211187</v>
+      </c>
+      <c r="E256" t="n">
+        <v>173300</v>
+      </c>
+      <c r="F256" t="n">
+        <v>36598.7071</v>
+      </c>
+      <c r="G256" t="n">
+        <v>90</v>
+      </c>
+      <c r="H256" t="n">
+        <v>248.34</v>
+      </c>
+      <c r="I256" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M256"/>
+  <dimension ref="A1:M260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13444,6 +13444,210 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>33780</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>KT&amp;G</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>286152</v>
+      </c>
+      <c r="E257" t="n">
+        <v>186700</v>
+      </c>
+      <c r="F257" t="n">
+        <v>53424.5784</v>
+      </c>
+      <c r="G257" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="H257" t="n">
+        <v>34.61</v>
+      </c>
+      <c r="I257" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>담배 제조업</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>144960</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>2749138</v>
+      </c>
+      <c r="E258" t="n">
+        <v>14580</v>
+      </c>
+      <c r="F258" t="n">
+        <v>40082.43204</v>
+      </c>
+      <c r="G258" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="H258" t="n">
+        <v>119.58</v>
+      </c>
+      <c r="I258" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>425420</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>474819</v>
+      </c>
+      <c r="E259" t="n">
+        <v>76200</v>
+      </c>
+      <c r="F259" t="n">
+        <v>36181.2078</v>
+      </c>
+      <c r="G259" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="H259" t="n">
+        <v>84.95</v>
+      </c>
+      <c r="I259" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>92870</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>엑시콘</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>570604</v>
+      </c>
+      <c r="E260" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F260" t="n">
+        <v>33095.032</v>
+      </c>
+      <c r="G260" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="H260" t="n">
+        <v>300.55</v>
+      </c>
+      <c r="I260" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M260"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13648,6 +13648,565 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>4413208</v>
+      </c>
+      <c r="E261" t="n">
+        <v>190100</v>
+      </c>
+      <c r="F261" t="n">
+        <v>838950.8408</v>
+      </c>
+      <c r="G261" t="n">
+        <v>80</v>
+      </c>
+      <c r="H261" t="n">
+        <v>153.47</v>
+      </c>
+      <c r="I261" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>53800</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>안랩</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1205087</v>
+      </c>
+      <c r="E262" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F262" t="n">
+        <v>133644.1483</v>
+      </c>
+      <c r="G262" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H262" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="I262" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>306394</v>
+      </c>
+      <c r="E263" t="n">
+        <v>193000</v>
+      </c>
+      <c r="F263" t="n">
+        <v>59134.042</v>
+      </c>
+      <c r="G263" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="H263" t="n">
+        <v>267.62</v>
+      </c>
+      <c r="I263" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>92870</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>엑시콘</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>794077</v>
+      </c>
+      <c r="E264" t="n">
+        <v>67000</v>
+      </c>
+      <c r="F264" t="n">
+        <v>53203.159</v>
+      </c>
+      <c r="G264" t="n">
+        <v>95</v>
+      </c>
+      <c r="H264" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="I264" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K264" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>425420</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>602865</v>
+      </c>
+      <c r="E265" t="n">
+        <v>84700</v>
+      </c>
+      <c r="F265" t="n">
+        <v>51062.6655</v>
+      </c>
+      <c r="G265" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="H265" t="n">
+        <v>110.96</v>
+      </c>
+      <c r="I265" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="K265" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>80580</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1686164</v>
+      </c>
+      <c r="E266" t="n">
+        <v>29700</v>
+      </c>
+      <c r="F266" t="n">
+        <v>50079.0708</v>
+      </c>
+      <c r="G266" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H266" t="n">
+        <v>200.91</v>
+      </c>
+      <c r="I266" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="K266" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>144960</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>2838693</v>
+      </c>
+      <c r="E267" t="n">
+        <v>15400</v>
+      </c>
+      <c r="F267" t="n">
+        <v>43715.8722</v>
+      </c>
+      <c r="G267" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="H267" t="n">
+        <v>143.29</v>
+      </c>
+      <c r="I267" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K267" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>36540</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>4212888</v>
+      </c>
+      <c r="E268" t="n">
+        <v>8980</v>
+      </c>
+      <c r="F268" t="n">
+        <v>37831.73424</v>
+      </c>
+      <c r="G268" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="H268" t="n">
+        <v>107.63</v>
+      </c>
+      <c r="I268" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="K268" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>128257</v>
+      </c>
+      <c r="E269" t="n">
+        <v>275000</v>
+      </c>
+      <c r="F269" t="n">
+        <v>35270.675</v>
+      </c>
+      <c r="G269" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="H269" t="n">
+        <v>435.02</v>
+      </c>
+      <c r="I269" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+        </is>
+      </c>
+      <c r="K269" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>78350</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>한양디지텍</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>846194</v>
+      </c>
+      <c r="E270" t="n">
+        <v>41000</v>
+      </c>
+      <c r="F270" t="n">
+        <v>34693.954</v>
+      </c>
+      <c r="G270" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="H270" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="I270" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="K270" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>64290</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>530405</v>
+      </c>
+      <c r="E271" t="n">
+        <v>63700</v>
+      </c>
+      <c r="F271" t="n">
+        <v>33786.7985</v>
+      </c>
+      <c r="G271" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H271" t="n">
+        <v>290.32</v>
+      </c>
+      <c r="I271" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K271" t="n">
+        <v>-64.40000000000001</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14207,6 +14207,361 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1110295</v>
+      </c>
+      <c r="E272" t="n">
+        <v>538000</v>
+      </c>
+      <c r="F272" t="n">
+        <v>597338.71</v>
+      </c>
+      <c r="G272" t="n">
+        <v>74</v>
+      </c>
+      <c r="H272" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>일차전지 및 이차전지 제조업</t>
+        </is>
+      </c>
+      <c r="K272" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>810</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>삼성화재</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>126997</v>
+      </c>
+      <c r="E273" t="n">
+        <v>651000</v>
+      </c>
+      <c r="F273" t="n">
+        <v>82675.04700000001</v>
+      </c>
+      <c r="G273" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="H273" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="I273" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>보험업</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>33780</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>KT&amp;G</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>335251</v>
+      </c>
+      <c r="E274" t="n">
+        <v>193100</v>
+      </c>
+      <c r="F274" t="n">
+        <v>64736.9681</v>
+      </c>
+      <c r="G274" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="H274" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="I274" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>담배 제조업</t>
+        </is>
+      </c>
+      <c r="K274" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>92870</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>엑시콘</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>653014</v>
+      </c>
+      <c r="E275" t="n">
+        <v>65300</v>
+      </c>
+      <c r="F275" t="n">
+        <v>42641.8142</v>
+      </c>
+      <c r="G275" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="H275" t="n">
+        <v>335.33</v>
+      </c>
+      <c r="I275" t="n">
+        <v>-3.97</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K275" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>144960</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>2559049</v>
+      </c>
+      <c r="E276" t="n">
+        <v>15250</v>
+      </c>
+      <c r="F276" t="n">
+        <v>39025.49725</v>
+      </c>
+      <c r="G276" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H276" t="n">
+        <v>127.27</v>
+      </c>
+      <c r="I276" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K276" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>425420</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>364109</v>
+      </c>
+      <c r="E277" t="n">
+        <v>85700</v>
+      </c>
+      <c r="F277" t="n">
+        <v>31204.1413</v>
+      </c>
+      <c r="G277" t="n">
+        <v>75</v>
+      </c>
+      <c r="H277" t="n">
+        <v>107.51</v>
+      </c>
+      <c r="I277" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="K277" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>80580</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1080016</v>
+      </c>
+      <c r="E278" t="n">
+        <v>27950</v>
+      </c>
+      <c r="F278" t="n">
+        <v>30186.4472</v>
+      </c>
+      <c r="G278" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="H278" t="n">
+        <v>180.62</v>
+      </c>
+      <c r="I278" t="n">
+        <v>-6.83</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="K278" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M278"/>
+  <dimension ref="A1:M280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14562,6 +14562,108 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>754028</v>
+      </c>
+      <c r="E279" t="n">
+        <v>543000</v>
+      </c>
+      <c r="F279" t="n">
+        <v>409437.204</v>
+      </c>
+      <c r="G279" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="H279" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>일차전지 및 이차전지 제조업</t>
+        </is>
+      </c>
+      <c r="K279" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>53800</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>안랩</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>1090537</v>
+      </c>
+      <c r="E280" t="n">
+        <v>118100</v>
+      </c>
+      <c r="F280" t="n">
+        <v>128792.4197</v>
+      </c>
+      <c r="G280" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H280" t="n">
+        <v>99.16</v>
+      </c>
+      <c r="I280" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="K280" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
